--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_246_R25.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_246_R25.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.9181</v>
+        <v>4.0435</v>
       </c>
       <c r="E2" t="n">
-        <v>4.4185</v>
+        <v>4.6112</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.5004</v>
+        <v>-0.5676</v>
       </c>
       <c r="G2" t="n">
         <v>4.9738</v>
@@ -610,13 +610,13 @@
         <v>1.3917</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.6071</v>
+        <v>-0.4817</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.8883</v>
+        <v>-0.6956</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2812</v>
+        <v>0.2139</v>
       </c>
       <c r="V2" t="n">
         <v>-1.6083</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. NEBO</t>
+          <t>Z. LEDAY</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.6729</v>
+        <v>3.8963</v>
       </c>
       <c r="E3" t="n">
-        <v>3.0118</v>
+        <v>2.7945</v>
       </c>
       <c r="F3" t="n">
-        <v>0.661</v>
+        <v>1.1018</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0318</v>
+        <v>-0.2261</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4499</v>
+        <v>-1.1094</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4182</v>
+        <v>0.8833</v>
       </c>
       <c r="J3" t="n">
-        <v>1.015</v>
+        <v>0.9144</v>
       </c>
       <c r="K3" t="n">
-        <v>0.9046</v>
+        <v>-0.6548</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1104</v>
+        <v>1.5692</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.9833</v>
+        <v>-1.1405</v>
       </c>
       <c r="N3" t="n">
         <v>-0.4547</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.5286</v>
+        <v>-0.6859</v>
       </c>
       <c r="P3" t="n">
-        <v>0.232</v>
+        <v>1.3917</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>1.3917</v>
       </c>
       <c r="S3" t="n">
-        <v>2.1952</v>
+        <v>1.1224</v>
       </c>
       <c r="T3" t="n">
-        <v>1.9426</v>
+        <v>0.13</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2526</v>
+        <v>0.9923999999999999</v>
       </c>
       <c r="V3" t="n">
-        <v>1.214</v>
+        <v>1.6083</v>
       </c>
       <c r="W3" t="n">
-        <v>1.214</v>
+        <v>1.7501</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Z. LEDAY</t>
+          <t>J. NEBO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.5514</v>
+        <v>2.7525</v>
       </c>
       <c r="E4" t="n">
-        <v>2.248</v>
+        <v>1.789</v>
       </c>
       <c r="F4" t="n">
-        <v>1.3034</v>
+        <v>0.9635</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.2261</v>
+        <v>0.0318</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.1094</v>
+        <v>0.4499</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8833</v>
+        <v>-0.4182</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9144</v>
+        <v>1.015</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.6548</v>
+        <v>0.9046</v>
       </c>
       <c r="L4" t="n">
-        <v>1.5692</v>
+        <v>0.1104</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.1405</v>
+        <v>-0.9833</v>
       </c>
       <c r="N4" t="n">
         <v>-0.4547</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.6859</v>
+        <v>-0.5286</v>
       </c>
       <c r="P4" t="n">
-        <v>1.3917</v>
+        <v>0.232</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R4" t="n">
         <v>1.3917</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7776</v>
+        <v>1.2748</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4165</v>
+        <v>0.7198</v>
       </c>
       <c r="U4" t="n">
-        <v>1.194</v>
+        <v>0.5551</v>
       </c>
       <c r="V4" t="n">
-        <v>1.6083</v>
+        <v>1.214</v>
       </c>
       <c r="W4" t="n">
-        <v>1.7501</v>
+        <v>1.214</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.0063</v>
+        <v>2.0138</v>
       </c>
       <c r="E5" t="n">
-        <v>1.9868</v>
+        <v>2.0615</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0195</v>
+        <v>-0.0477</v>
       </c>
       <c r="G5" t="n">
         <v>4.4404</v>
@@ -844,13 +844,13 @@
         <v>1.3917</v>
       </c>
       <c r="S5" t="n">
-        <v>0.7257</v>
+        <v>0.7332</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0712</v>
+        <v>0.1458</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6546</v>
+        <v>0.5874</v>
       </c>
       <c r="V5" t="n">
         <v>-1.0722</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4638</v>
+        <v>1.2456</v>
       </c>
       <c r="E6" t="n">
-        <v>1.0912</v>
+        <v>1.2092</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3726</v>
+        <v>0.0365</v>
       </c>
       <c r="G6" t="n">
         <v>-0.0231</v>
@@ -922,13 +922,13 @@
         <v>0.9278</v>
       </c>
       <c r="S6" t="n">
-        <v>0.9867</v>
+        <v>0.7685999999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0158</v>
+        <v>0.1338</v>
       </c>
       <c r="U6" t="n">
-        <v>0.9709</v>
+        <v>0.6348</v>
       </c>
       <c r="V6" t="n">
         <v>1.8919</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2424</v>
+        <v>-0.0572</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2299</v>
+        <v>-0.112</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0124</v>
+        <v>0.0548</v>
       </c>
       <c r="G7" t="n">
         <v>0.11</v>
@@ -1000,13 +1000,13 @@
         <v>0.9278</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.0482</v>
+        <v>-0.863</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5975</v>
+        <v>-0.4795</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4507</v>
+        <v>-0.3835</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. BOOKER</t>
+          <t>S. SHIELDS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.7394</v>
+        <v>-1.7867</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.3238</v>
+        <v>-0.4798</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4156</v>
+        <v>-1.3069</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.9095</v>
+        <v>-2.6023</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4322</v>
+        <v>-0.2701</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.3417</v>
+        <v>-2.3322</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.2627</v>
+        <v>-1.5012</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3396</v>
+        <v>0.1953</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6022999999999999</v>
+        <v>-1.6965</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.6468</v>
+        <v>-1.1011</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0926</v>
+        <v>-0.4655</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.7393999999999999</v>
+        <v>-0.6356000000000001</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.4639</v>
+        <v>1.3917</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.3917</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9278</v>
+        <v>1.3917</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3659</v>
+        <v>0.6379</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1889</v>
+        <v>-0.0507</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5548</v>
+        <v>0.6886</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-1.214</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1418</v>
+        <v>1.0722</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.1418</v>
+        <v>-2.2862</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. SHIELDS</t>
+          <t>D. BOOKER</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.3503</v>
+        <v>-1.9759</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.1442</v>
+        <v>-1.7956</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.2061</v>
+        <v>-0.1803</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.6023</v>
+        <v>-0.9095</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2701</v>
+        <v>0.4322</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.3322</v>
+        <v>-1.3417</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.5012</v>
+        <v>-0.2627</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1953</v>
+        <v>0.3396</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.6965</v>
+        <v>-0.6022999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.1011</v>
+        <v>-0.6468</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.4655</v>
+        <v>0.0926</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.6356000000000001</v>
+        <v>-0.7393999999999999</v>
       </c>
       <c r="P10" t="n">
-        <v>1.3917</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-1.3917</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3917</v>
+        <v>0.9278</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0742</v>
+        <v>-0.6025</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7151999999999999</v>
+        <v>-0.2829</v>
       </c>
       <c r="U10" t="n">
-        <v>0.7894</v>
+        <v>-0.3196</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.214</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.0722</v>
+        <v>0.1418</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.2862</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.5108</v>
+        <v>-2.9889</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.5357</v>
+        <v>-2.1819</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.9751</v>
+        <v>-0.8070000000000001</v>
       </c>
       <c r="G11" t="n">
         <v>-1.9244</v>
@@ -1312,13 +1312,13 @@
         <v>1.1598</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.0477</v>
+        <v>-0.5258</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6642</v>
+        <v>-0.3104</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3835</v>
+        <v>-0.2155</v>
       </c>
       <c r="V11" t="n">
         <v>-1.4665</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>6.299199999999999</v>
+        <v>6.6726</v>
       </c>
       <c r="E12" t="n">
-        <v>6.503299999999999</v>
+        <v>6.876699999999998</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2040999999999998</v>
+        <v>-0.2039</v>
       </c>
       <c r="G12" t="n">
         <v>3.093599999999999</v>
@@ -1366,10 +1366,10 @@
         <v>11.2437</v>
       </c>
       <c r="K12" t="n">
-        <v>7.530399999999999</v>
+        <v>7.5304</v>
       </c>
       <c r="L12" t="n">
-        <v>3.713199999999998</v>
+        <v>3.713200000000001</v>
       </c>
       <c r="M12" t="n">
         <v>-8.1503</v>
@@ -1378,7 +1378,7 @@
         <v>-1.8106</v>
       </c>
       <c r="O12" t="n">
-        <v>-6.339799999999999</v>
+        <v>-6.3398</v>
       </c>
       <c r="P12" t="n">
         <v>2.319599999999999</v>
@@ -1390,16 +1390,16 @@
         <v>11.5976</v>
       </c>
       <c r="S12" t="n">
-        <v>1.533199999999999</v>
+        <v>1.9066</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.1379</v>
+        <v>-0.7644</v>
       </c>
       <c r="U12" t="n">
-        <v>2.6711</v>
+        <v>2.671</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.6468000000000003</v>
+        <v>-0.6468</v>
       </c>
       <c r="W12" t="n">
         <v>5.6757</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.4562</v>
+        <v>2.4911</v>
       </c>
       <c r="E13" t="n">
-        <v>1.0812</v>
+        <v>1.553</v>
       </c>
       <c r="F13" t="n">
-        <v>1.375</v>
+        <v>0.9381</v>
       </c>
       <c r="G13" t="n">
         <v>2.5862</v>
@@ -1468,13 +1468,13 @@
         <v>0.9278</v>
       </c>
       <c r="S13" t="n">
-        <v>0.6717</v>
+        <v>0.7066</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8804</v>
+        <v>-0.4086</v>
       </c>
       <c r="U13" t="n">
-        <v>1.5521</v>
+        <v>1.1152</v>
       </c>
       <c r="V13" t="n">
         <v>-1.4975</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.9376</v>
+        <v>1.668</v>
       </c>
       <c r="E14" t="n">
-        <v>3.2736</v>
+        <v>2.5659</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.3361</v>
+        <v>-0.8979</v>
       </c>
       <c r="G14" t="n">
         <v>0.4619</v>
@@ -1546,13 +1546,13 @@
         <v>0.9278</v>
       </c>
       <c r="S14" t="n">
-        <v>0.7798</v>
+        <v>0.5102</v>
       </c>
       <c r="T14" t="n">
-        <v>0.8417</v>
+        <v>0.134</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0619</v>
+        <v>0.3763</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.1281</v>
+        <v>1.3532</v>
       </c>
       <c r="E15" t="n">
-        <v>1.7115</v>
+        <v>1.4756</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.5834</v>
+        <v>-0.1224</v>
       </c>
       <c r="G15" t="n">
         <v>0.7896</v>
@@ -1624,13 +1624,13 @@
         <v>1.3917</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2851</v>
+        <v>-0.06</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4832</v>
+        <v>-0.7191</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1981</v>
+        <v>0.6592</v>
       </c>
       <c r="V15" t="n">
         <v>-0.5361</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0827</v>
+        <v>0.3555</v>
       </c>
       <c r="E16" t="n">
         <v>0.7901</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.8728</v>
+        <v>-0.4346</v>
       </c>
       <c r="G16" t="n">
         <v>0.4139</v>
@@ -1702,13 +1702,13 @@
         <v>1.1598</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2842</v>
+        <v>0.7224</v>
       </c>
       <c r="T16" t="n">
         <v>0.3462</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0619</v>
+        <v>0.3763</v>
       </c>
       <c r="V16" t="n">
         <v>2.0026</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.6692</v>
+        <v>-0.394</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.8327</v>
+        <v>-0.7148</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1635</v>
+        <v>0.3207</v>
       </c>
       <c r="G17" t="n">
         <v>0.3283</v>
@@ -1780,13 +1780,13 @@
         <v>0.9278</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.8531</v>
+        <v>-0.5779</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.2617</v>
+        <v>-1.1437</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4086</v>
+        <v>0.5658</v>
       </c>
       <c r="V17" t="n">
         <v>-1.0722</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>I. BONGA</t>
+          <t>S. BROWN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.7885</v>
+        <v>-0.8183</v>
       </c>
       <c r="E18" t="n">
-        <v>0.4219</v>
+        <v>-1.9142</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.2104</v>
+        <v>1.0959</v>
       </c>
       <c r="G18" t="n">
-        <v>-3.0172</v>
+        <v>-1.6595</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.8366</v>
+        <v>0.0035</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1806</v>
+        <v>-1.663</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.8763</v>
+        <v>-0.5365</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.3843</v>
+        <v>1.1735</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.4919</v>
+        <v>-1.71</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.1409</v>
+        <v>-1.123</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.4522</v>
+        <v>-1.17</v>
       </c>
       <c r="O18" t="n">
-        <v>0.3113</v>
+        <v>0.047</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9278</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.4639</v>
+        <v>-2.7834</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3917</v>
+        <v>1.6237</v>
       </c>
       <c r="S18" t="n">
-        <v>0.7648</v>
+        <v>-0.1434</v>
       </c>
       <c r="T18" t="n">
-        <v>0.6176</v>
+        <v>-0.7387</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1472</v>
+        <v>0.5953000000000001</v>
       </c>
       <c r="V18" t="n">
-        <v>0.5361</v>
+        <v>2.1444</v>
       </c>
       <c r="W18" t="n">
         <v>2.1444</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.6083</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>U. MIJAILOVIC</t>
+          <t>I. BONGA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.2899</v>
+        <v>-0.8957000000000001</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.0211</v>
+        <v>-0.1679</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.2689</v>
+        <v>-0.7278</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.3974</v>
+        <v>-3.0172</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.4873</v>
+        <v>-2.8366</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.9101</v>
+        <v>-0.1806</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0536</v>
+        <v>-1.8763</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0168</v>
+        <v>-1.3843</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0368</v>
+        <v>-0.4919</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.451</v>
+        <v>-1.1409</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.5041</v>
+        <v>-1.4522</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.9469</v>
+        <v>0.3113</v>
       </c>
       <c r="P19" t="n">
-        <v>0.232</v>
+        <v>0.9278</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-0.4639</v>
       </c>
       <c r="R19" t="n">
-        <v>0.232</v>
+        <v>1.3917</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0523</v>
+        <v>0.6576</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0747</v>
+        <v>0.0279</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0224</v>
+        <v>0.6297</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.0722</v>
+        <v>0.5361</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2.1444</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.0722</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S. BROWN</t>
+          <t>U. MIJAILOVIC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.3732</v>
+        <v>-2.1384</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.5039</v>
+        <v>0.0969</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1307</v>
+        <v>-2.2353</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.6595</v>
+        <v>-1.3974</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0035</v>
+        <v>-0.4873</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.663</v>
+        <v>-0.9101</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.5365</v>
+        <v>0.0536</v>
       </c>
       <c r="K20" t="n">
-        <v>1.1735</v>
+        <v>0.0168</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.71</v>
+        <v>0.0368</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.123</v>
+        <v>-1.451</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.17</v>
+        <v>-0.5041</v>
       </c>
       <c r="O20" t="n">
-        <v>0.047</v>
+        <v>-0.9469</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.1598</v>
+        <v>0.232</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.7834</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.6237</v>
+        <v>0.232</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.6983</v>
+        <v>0.0993</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.3285</v>
+        <v>0.0433</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3699</v>
+        <v>0.056</v>
       </c>
       <c r="V20" t="n">
-        <v>2.1444</v>
+        <v>-1.0722</v>
       </c>
       <c r="W20" t="n">
-        <v>2.1444</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.6175</v>
+        <v>-4.7754</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.3221</v>
+        <v>-3.0862</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.2954</v>
+        <v>-1.6892</v>
       </c>
       <c r="G21" t="n">
         <v>-1.5991</v>
@@ -2092,13 +2092,13 @@
         <v>0.6959</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.1448</v>
+        <v>-0.3027</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4481</v>
+        <v>-0.2122</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6967</v>
+        <v>-0.0905</v>
       </c>
       <c r="V21" t="n">
         <v>0.1418</v>
@@ -2125,22 +2125,22 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.2991</v>
+        <v>-3.154000000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>0.5985</v>
+        <v>0.5983999999999998</v>
       </c>
       <c r="F22" t="n">
-        <v>-6.897799999999999</v>
+        <v>-3.7525</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.093299999999999</v>
+        <v>-3.0933</v>
       </c>
       <c r="H22" t="n">
-        <v>-5.7199</v>
+        <v>-5.719899999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>2.626599999999999</v>
+        <v>2.6266</v>
       </c>
       <c r="J22" t="n">
         <v>8.1502</v>
@@ -2170,13 +2170,13 @@
         <v>9.2782</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.5331</v>
+        <v>1.6121</v>
       </c>
       <c r="T22" t="n">
-        <v>-2.6711</v>
+        <v>-2.6709</v>
       </c>
       <c r="U22" t="n">
-        <v>1.138</v>
+        <v>4.283300000000001</v>
       </c>
       <c r="V22" t="n">
         <v>0.6469000000000001</v>
